--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,10 +489,8 @@
           <t>2026-09-20 07:02:09</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -504,10 +502,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+      <c r="E2" t="n">
+        <v>4500011739</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -541,6 +537,303 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:45:26</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>100</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:45:26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:16:44</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:16:44</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>24</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:16:44</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>24</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>100</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,10 +660,8 @@
           <t>2026-09-20 08:16:44</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B5" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -675,10 +673,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+      <c r="E5" t="n">
+        <v>4500011739</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -721,10 +717,8 @@
           <t>2026-09-20 08:16:44</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B6" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -736,10 +730,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+      <c r="E6" t="n">
+        <v>4500011739</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -782,10 +774,8 @@
           <t>2026-09-20 08:16:44</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B7" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -797,10 +787,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+      <c r="E7" t="n">
+        <v>4500011739</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -834,6 +822,1272 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:31:57</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>13</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>100</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:31:57</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>100</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:31:57</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>17</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>100</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:31:57</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>22</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>650000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:31:57</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>650000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>100</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:31:57</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>23</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>600000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>100</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:31:57</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>600000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>100</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:14:35</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>100</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:14:35</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>100</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:14:35</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>100</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:14:35</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>100</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:14:35</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>100</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:14:35</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>100</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:26:04</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>100</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:26:04</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:26:04</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>25</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>100</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:26:04</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>100</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:26:04</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>25</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L25" t="n">
+        <v>100</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:26:04</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>22</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:33:45</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>100</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:33:45</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>100</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:33:45</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>21</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>100</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1914,10 +1914,8 @@
           <t>2026-09-20 11:33:45</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B27" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1929,10 +1927,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+      <c r="E27" t="n">
+        <v>4500011739</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1975,10 +1971,8 @@
           <t>2026-09-20 11:33:45</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B28" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1990,10 +1984,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+      <c r="E28" t="n">
+        <v>4500011739</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2036,10 +2028,8 @@
           <t>2026-09-20 11:33:45</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B29" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2051,10 +2041,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+      <c r="E29" t="n">
+        <v>4500011739</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2088,6 +2076,580 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-21 09:24:55</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>100</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:45:33</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>100</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:16</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>250</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>100</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:16</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>200</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L33" t="n">
+        <v>100</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:16</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>50</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L34" t="n">
+        <v>100</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:16</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>50</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L35" t="n">
+        <v>100</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:16</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>50</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L36" t="n">
+        <v>100</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:16</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>50</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L37" t="n">
+        <v>100</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:16</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>115</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L38" t="n">
+        <v>100</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:58:54</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>5054500</v>
+      </c>
+      <c r="L39" t="n">
+        <v>100</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -1227,7 +1227,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 10:14:35</t>
+          <t>2026-09-20 10:26:04</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1253,38 +1253,38 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.48</v>
+        <v>25</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>25000000</v>
+        <v>1600000</v>
       </c>
       <c r="L15" t="n">
         <v>100</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 10:14:35</t>
+          <t>2026-09-20 10:26:04</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1310,38 +1310,38 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.48</v>
+        <v>15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>17500000</v>
+        <v>1600000</v>
       </c>
       <c r="L16" t="n">
         <v>100</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 10:14:35</t>
+          <t>2026-09-20 10:26:04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1367,38 +1367,38 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 10:14:35</t>
+          <t>2026-09-20 10:26:04</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1424,38 +1424,38 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.74</v>
+        <v>4</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="L18" t="n">
         <v>100</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 10:14:35</t>
+          <t>2026-09-20 10:26:04</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1481,38 +1481,38 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="L19" t="n">
         <v>100</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 10:14:35</t>
+          <t>2026-09-20 10:26:04</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1538,38 +1538,38 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.74</v>
+        <v>22</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="L20" t="n">
         <v>100</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 10:26:04</t>
+          <t>2026-09-20 11:33:45</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1595,16 +1595,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1612,21 +1612,21 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="L21" t="n">
         <v>100</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20 10:26:04</t>
+          <t>2026-09-20 11:33:45</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1652,16 +1652,16 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="L22" t="n">
         <v>100</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20 10:26:04</t>
+          <t>2026-09-20 11:33:45</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1709,16 +1709,16 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1600000</v>
+        <v>2750000</v>
       </c>
       <c r="L23" t="n">
         <v>100</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20 10:26:04</t>
+          <t>2026-09-21 09:24:55</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1766,38 +1766,38 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1600000</v>
+        <v>12500000</v>
       </c>
       <c r="L24" t="n">
         <v>100</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20 10:26:04</t>
+          <t>2026-09-21 11:45:33</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1823,38 +1823,38 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>316.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="L25" t="n">
         <v>100</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-20 10:26:04</t>
+          <t>2026-09-21 12:41:16</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1880,38 +1880,38 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="L26" t="n">
         <v>100</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20 11:33:45</t>
+          <t>2026-09-21 12:41:16</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1937,38 +1937,38 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="L27" t="n">
         <v>100</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20 11:33:45</t>
+          <t>2026-09-21 12:41:16</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1994,38 +1994,38 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="L28" t="n">
         <v>100</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-20 11:33:45</t>
+          <t>2026-09-21 12:41:16</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2051,38 +2051,38 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>2750000</v>
+        <v>25000</v>
       </c>
       <c r="L29" t="n">
         <v>100</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21 09:24:55</t>
+          <t>2026-09-21 12:41:16</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2108,16 +2108,16 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2125,21 +2125,21 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>12500000</v>
+        <v>25000</v>
       </c>
       <c r="L30" t="n">
         <v>100</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-21 11:45:33</t>
+          <t>2026-09-21 12:41:16</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2165,20 +2165,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>316.8</v>
+        <v>50</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2246,14 +2246,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
+          <t>2026-09-21 12:58:54</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>19 Sep 2026</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2279,46 +2279,48 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>25000</v>
+        <v>5054500</v>
       </c>
       <c r="L33" t="n">
         <v>100</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:55:16</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2326,8 +2328,10 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2336,46 +2340,48 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>25000</v>
+        <v>25000000</v>
       </c>
       <c r="L34" t="n">
         <v>100</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:55:16</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2383,8 +2389,10 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2393,46 +2401,48 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>25000</v>
+        <v>17500000</v>
       </c>
       <c r="L35" t="n">
         <v>100</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:55:16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2440,8 +2450,10 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2450,46 +2462,48 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>50</v>
+        <v>0.74</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="L36" t="n">
         <v>100</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:55:16</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2497,8 +2511,10 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2507,46 +2523,48 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>50</v>
+        <v>0.74</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="L37" t="n">
         <v>100</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>7201250141</v>
+          <t>2026-09-22 10:55:16</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2554,8 +2572,10 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2564,38 +2584,38 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>115</v>
+        <v>0.74</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>25000</v>
+        <v>15000000</v>
       </c>
       <c r="L38" t="n">
         <v>100</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-21 12:58:54</t>
+          <t>2026-09-22 10:55:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2605,17 +2625,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2625,31 +2645,31 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>5054500</v>
+        <v>15000000</v>
       </c>
       <c r="L39" t="n">
         <v>100</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -1854,7 +1854,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
+          <t>2026-09-21 12:58:54</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>19 Sep 2026</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1880,38 +1880,38 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>25000</v>
+        <v>5054500</v>
       </c>
       <c r="L26" t="n">
         <v>100</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
+          <t>2026-09-22 10:55:16</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1937,38 +1937,38 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>200</v>
+        <v>0.48</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>25000</v>
+        <v>25000000</v>
       </c>
       <c r="L27" t="n">
         <v>100</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
+          <t>2026-09-22 10:55:16</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1994,38 +1994,38 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>25000</v>
+        <v>17500000</v>
       </c>
       <c r="L28" t="n">
         <v>100</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
+          <t>2026-09-22 10:55:16</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2051,38 +2051,38 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>50</v>
+        <v>0.74</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="L29" t="n">
         <v>100</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
+          <t>2026-09-22 10:55:16</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2108,38 +2108,38 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>50</v>
+        <v>0.74</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="L30" t="n">
         <v>100</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
+          <t>2026-09-22 10:55:16</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2165,38 +2165,38 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>50</v>
+        <v>0.74</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>25000</v>
+        <v>15000000</v>
       </c>
       <c r="L31" t="n">
         <v>100</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-21 12:41:16</t>
+          <t>2026-09-22 10:55:16</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2222,55 +2222,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>115</v>
+        <v>0.74</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>25000</v>
+        <v>15000000</v>
       </c>
       <c r="L32" t="n">
         <v>100</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-21 12:58:54</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>7201250141</v>
+          <t>2026-09-28 11:29:55</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2279,38 +2283,38 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>5054500</v>
+        <v>25000</v>
       </c>
       <c r="L33" t="n">
         <v>100</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-22 10:55:16</t>
+          <t>2026-09-28 11:29:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2320,7 +2324,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2330,7 +2334,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2340,38 +2344,38 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.48</v>
+        <v>200</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>25000000</v>
+        <v>25000</v>
       </c>
       <c r="L34" t="n">
         <v>100</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-22 10:55:16</t>
+          <t>2026-09-28 11:29:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2381,7 +2385,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2391,7 +2395,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2401,38 +2405,38 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.48</v>
+        <v>50</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>17500000</v>
+        <v>25000</v>
       </c>
       <c r="L35" t="n">
         <v>100</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-22 10:55:16</t>
+          <t>2026-09-28 11:29:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2442,7 +2446,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2452,7 +2456,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2462,38 +2466,38 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.74</v>
+        <v>50</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>60000000</v>
+        <v>25000</v>
       </c>
       <c r="L36" t="n">
         <v>100</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-22 10:55:16</t>
+          <t>2026-09-28 11:29:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2503,7 +2507,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2513,7 +2517,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2523,38 +2527,38 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.74</v>
+        <v>50</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>60000000</v>
+        <v>25000</v>
       </c>
       <c r="L37" t="n">
         <v>100</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-22 10:55:16</t>
+          <t>2026-09-28 11:29:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2564,7 +2568,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2574,7 +2578,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2584,38 +2588,38 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.74</v>
+        <v>50</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>15000000</v>
+        <v>25000</v>
       </c>
       <c r="L38" t="n">
         <v>100</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-22 10:55:16</t>
+          <t>2026-09-28 11:29:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2625,7 +2629,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2635,7 +2639,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2645,31 +2649,31 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.74</v>
+        <v>115</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>15000000</v>
+        <v>25000</v>
       </c>
       <c r="L39" t="n">
         <v>100</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2256,10 +2256,8 @@
           <t>2026-09-28 11:29:55</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B33" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2271,10 +2269,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E33" t="n">
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2317,10 +2313,8 @@
           <t>2026-09-28 11:29:55</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B34" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2332,10 +2326,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E34" t="n">
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2378,10 +2370,8 @@
           <t>2026-09-28 11:29:55</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B35" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2393,10 +2383,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E35" t="n">
+        <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2439,10 +2427,8 @@
           <t>2026-09-28 11:29:55</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B36" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2454,10 +2440,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E36" t="n">
+        <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2500,10 +2484,8 @@
           <t>2026-09-28 11:29:55</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B37" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2515,10 +2497,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E37" t="n">
+        <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2561,10 +2541,8 @@
           <t>2026-09-28 11:29:55</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B38" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2576,10 +2554,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E38" t="n">
+        <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2622,10 +2598,8 @@
           <t>2026-09-28 11:29:55</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B39" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2637,10 +2611,8 @@
           <t>31 Aug 2026</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E39" t="n">
+        <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2674,6 +2646,673 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:24:08</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>30 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>48</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>100</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:48</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Aqua 600 ml</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>240</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>7500</v>
+      </c>
+      <c r="L41" t="n">
+        <v>100</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:48</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>24</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L42" t="n">
+        <v>100</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:48</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>24</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L43" t="n">
+        <v>100</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:48</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>48</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L44" t="n">
+        <v>100</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:48</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>48</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>84500</v>
+      </c>
+      <c r="L45" t="n">
+        <v>100</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:48</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Coca Cola</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>48</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L46" t="n">
+        <v>100</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:48</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Fanta</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>48</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L47" t="n">
+        <v>100</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:48</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>48</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L48" t="n">
+        <v>100</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>48</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L49" t="n">
+        <v>100</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:48</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>48</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L50" t="n">
+        <v>100</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,10 +2712,8 @@
           <t>2026-09-30 13:23:48</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B41" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2727,10 +2725,8 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E41" t="n">
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2773,10 +2769,8 @@
           <t>2026-09-30 13:23:48</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B42" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2788,10 +2782,8 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E42" t="n">
+        <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2834,10 +2826,8 @@
           <t>2026-09-30 13:23:48</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B43" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2849,10 +2839,8 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E43" t="n">
+        <v>0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2895,10 +2883,8 @@
           <t>2026-09-30 13:23:48</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B44" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2910,10 +2896,8 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E44" t="n">
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2956,10 +2940,8 @@
           <t>2026-09-30 13:23:48</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B45" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2971,10 +2953,8 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E45" t="n">
+        <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3017,10 +2997,8 @@
           <t>2026-09-30 13:23:48</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B46" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3032,10 +3010,8 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E46" t="n">
+        <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3078,10 +3054,8 @@
           <t>2026-09-30 13:23:48</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B47" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3093,10 +3067,8 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E47" t="n">
+        <v>0</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3139,10 +3111,8 @@
           <t>2026-09-30 13:23:48</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B48" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3154,10 +3124,8 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E48" t="n">
+        <v>0</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3200,10 +3168,8 @@
           <t>2026-09-30 13:23:48</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B49" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3215,10 +3181,8 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E49" t="n">
+        <v>0</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3261,10 +3225,8 @@
           <t>2026-09-30 13:23:48</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B50" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -3276,10 +3238,8 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E50" t="n">
+        <v>0</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3313,6 +3273,67 @@
       <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:43:13</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/WS/X/2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>02 Oct 2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>131650000</v>
+      </c>
+      <c r="L51" t="n">
+        <v>100</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3282,10 +3282,8 @@
           <t>2026-10-01 13:43:13</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B51" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3297,10 +3295,8 @@
           <t>02 Oct 2026</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E51" t="n">
+        <v>0</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3334,6 +3330,124 @@
       <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:15:52</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>036/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>10 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L52" t="n">
+        <v>100</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:38:44</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>46750000</v>
+      </c>
+      <c r="L53" t="n">
+        <v>100</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2709,7 +2709,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:48</t>
+          <t>2026-10-01 13:43:13</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>02 Oct 2026</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2735,38 +2735,38 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>7500</v>
+        <v>131650000</v>
       </c>
       <c r="L41" t="n">
         <v>100</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:48</t>
+          <t>2026-10-02 09:15:52</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2774,16 +2774,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2792,38 +2792,38 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>489.8</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>19500</v>
+        <v>25000</v>
       </c>
       <c r="L42" t="n">
         <v>100</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:48</t>
+          <t>2026-10-02 09:38:44</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2831,16 +2831,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2849,42 +2851,44 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>15600</v>
+        <v>46750000</v>
       </c>
       <c r="L43" t="n">
         <v>100</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:48</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2896,8 +2900,10 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>0</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2911,11 +2917,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2923,7 +2929,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>13000</v>
+        <v>32500</v>
       </c>
       <c r="L44" t="n">
         <v>100</v>
@@ -2937,11 +2943,13 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:48</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2953,8 +2961,10 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>0</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2972,7 +2982,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2994,11 +3004,13 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:48</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3010,8 +3022,10 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3025,11 +3039,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Coca Cola</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3037,7 +3051,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9750</v>
+        <v>26000</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
@@ -3051,11 +3065,13 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:48</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3067,8 +3083,10 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3082,15 +3100,15 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fanta</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3108,11 +3126,13 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:48</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3124,8 +3144,10 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3139,19 +3161,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="L48" t="n">
         <v>100</v>
@@ -3165,11 +3187,13 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:48</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3181,8 +3205,10 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3196,19 +3222,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="L49" t="n">
         <v>100</v>
@@ -3222,11 +3248,13 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:48</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -3238,8 +3266,10 @@
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>0</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3257,7 +3287,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3279,24 +3309,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-01 13:43:13</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>02 Oct 2026</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3305,16 +3339,16 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3322,38 +3356,42 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>131650000</v>
+        <v>19500</v>
       </c>
       <c r="L51" t="n">
         <v>100</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-02 09:15:52</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10 Sep 2026</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>4500011739</v>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3362,38 +3400,38 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>489.8</v>
+        <v>36</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>25000</v>
+        <v>32500</v>
       </c>
       <c r="L52" t="n">
         <v>100</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:44</t>
+          <t>2026-10-03 06:53:35</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3403,17 +3441,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3423,16 +3461,16 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3440,14 +3478,136 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>46750000</v>
+        <v>32500</v>
       </c>
       <c r="L53" t="n">
         <v>100</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>36</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L54" t="n">
+        <v>100</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:53:35</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>72</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L55" t="n">
+        <v>100</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2885,10 +2885,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B44" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2946,10 +2944,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B45" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -3007,10 +3003,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B46" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3068,10 +3062,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B47" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3129,10 +3121,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B48" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3190,10 +3180,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B49" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3251,10 +3239,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B50" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -3312,10 +3298,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B51" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3373,10 +3357,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B52" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -3434,10 +3416,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B53" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3495,10 +3475,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B54" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3556,10 +3534,8 @@
           <t>2026-10-03 06:53:35</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B55" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3608,6 +3584,738 @@
       <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Indocafe Coffemix Renteng</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L56" t="n">
+        <v>100</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>6</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>84500</v>
+      </c>
+      <c r="L57" t="n">
+        <v>100</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Nescafe Classic renteng</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>5</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L58" t="n">
+        <v>100</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>72</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L59" t="n">
+        <v>100</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L60" t="n">
+        <v>100</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>72</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L61" t="n">
+        <v>100</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>72</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L62" t="n">
+        <v>100</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>72</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L63" t="n">
+        <v>100</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>48</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L64" t="n">
+        <v>100</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>10</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L65" t="n">
+        <v>100</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>10</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L66" t="n">
+        <v>100</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>10</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L67" t="n">
+        <v>100</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3593,10 +3593,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B56" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3654,10 +3652,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B57" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3715,10 +3711,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B58" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3776,10 +3770,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B59" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3837,10 +3829,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B60" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3898,10 +3888,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B61" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3959,10 +3947,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B62" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -4020,10 +4006,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B63" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -4081,10 +4065,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B64" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -4142,10 +4124,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B65" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -4203,10 +4183,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B66" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -4264,10 +4242,8 @@
           <t>2026-10-03 12:00:10</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B67" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -4316,6 +4292,606 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:54:44</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>16</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L68" t="n">
+        <v>100</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:54:44</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L69" t="n">
+        <v>100</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:54:44</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L70" t="n">
+        <v>100</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:54:44</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>2</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L71" t="n">
+        <v>100</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:54:44</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="L72" t="n">
+        <v>100</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:08</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L73" t="n">
+        <v>100</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:08</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L74" t="n">
+        <v>100</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:08</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L75" t="n">
+        <v>100</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:08</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>105</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L76" t="n">
+        <v>100</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:04:08</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="L77" t="n">
+        <v>100</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1854,7 +1854,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21 12:58:54</t>
+          <t>2026-09-22 10:55:16</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1862,16 +1862,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1880,31 +1880,31 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>5054500</v>
+        <v>25000000</v>
       </c>
       <c r="L26" t="n">
         <v>100</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1954,14 +1954,14 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>25000000</v>
+        <v>17500000</v>
       </c>
       <c r="L27" t="n">
         <v>100</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
     </row>
@@ -1994,16 +1994,16 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2011,14 +2011,14 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="L28" t="n">
         <v>100</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2125,14 +2125,14 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="L30" t="n">
         <v>100</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-22 10:55:16</t>
+          <t>2026-09-28 11:29:55</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2222,31 +2222,31 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.74</v>
+        <v>250</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>15000000</v>
+        <v>25000</v>
       </c>
       <c r="L32" t="n">
         <v>100</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2588,14 +2588,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-28 11:29:55</t>
+          <t>2026-09-30 12:24:08</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2603,16 +2603,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>30 Aug 2026</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2621,38 +2621,38 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>25000</v>
+        <v>250000</v>
       </c>
       <c r="L39" t="n">
         <v>100</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-30 12:24:08</t>
+          <t>2026-10-01 13:43:13</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2660,16 +2660,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>30 Aug 2026</t>
+          <t>02 Oct 2026</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2678,38 +2678,38 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>250000</v>
+        <v>131650000</v>
       </c>
       <c r="L40" t="n">
         <v>100</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-01 13:43:13</t>
+          <t>2026-10-02 09:15:52</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2717,16 +2717,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>02 Oct 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2735,38 +2735,38 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>489.8</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>131650000</v>
+        <v>25000</v>
       </c>
       <c r="L41" t="n">
         <v>100</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-02 09:15:52</t>
+          <t>2026-10-02 09:38:44</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2774,16 +2774,18 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10 Sep 2026</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>4500011739</v>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2792,38 +2794,38 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>489.8</v>
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>25000</v>
+        <v>46750000</v>
       </c>
       <c r="L42" t="n">
         <v>100</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:44</t>
+          <t>2026-10-03 06:53:35</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2831,17 +2833,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2851,31 +2853,31 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>46750000</v>
+        <v>32500</v>
       </c>
       <c r="L43" t="n">
         <v>100</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
@@ -2915,7 +2917,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2927,7 +2929,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>32500</v>
+        <v>84500</v>
       </c>
       <c r="L44" t="n">
         <v>100</v>
@@ -2974,11 +2976,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2986,7 +2988,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>84500</v>
+        <v>26000</v>
       </c>
       <c r="L45" t="n">
         <v>100</v>
@@ -3033,11 +3035,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3045,7 +3047,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>26000</v>
+        <v>9750</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
@@ -3092,11 +3094,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3104,7 +3106,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="L47" t="n">
         <v>100</v>
@@ -3151,11 +3153,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3163,7 +3165,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="L48" t="n">
         <v>100</v>
@@ -3210,7 +3212,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3218,11 +3220,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>13000</v>
+        <v>9750</v>
       </c>
       <c r="L49" t="n">
         <v>100</v>
@@ -3269,7 +3271,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3281,7 +3283,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="L50" t="n">
         <v>100</v>
@@ -3328,11 +3330,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3340,7 +3342,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>19500</v>
+        <v>32500</v>
       </c>
       <c r="L51" t="n">
         <v>100</v>
@@ -3387,7 +3389,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3446,7 +3448,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3505,11 +3507,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3517,7 +3519,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>32500</v>
+        <v>15600</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
@@ -3531,7 +3533,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 12:00:10</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3539,12 +3541,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3564,26 +3566,26 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>15600</v>
+        <v>32500</v>
       </c>
       <c r="L55" t="n">
         <v>100</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
@@ -3623,11 +3625,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3635,7 +3637,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>32500</v>
+        <v>84500</v>
       </c>
       <c r="L56" t="n">
         <v>100</v>
@@ -3682,11 +3684,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3694,7 +3696,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>84500</v>
+        <v>26000</v>
       </c>
       <c r="L57" t="n">
         <v>100</v>
@@ -3741,11 +3743,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3753,7 +3755,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>26000</v>
+        <v>9750</v>
       </c>
       <c r="L58" t="n">
         <v>100</v>
@@ -3800,11 +3802,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3812,7 +3814,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="L59" t="n">
         <v>100</v>
@@ -3859,11 +3861,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3871,7 +3873,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="L60" t="n">
         <v>100</v>
@@ -3918,7 +3920,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -3930,7 +3932,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>13000</v>
+        <v>9750</v>
       </c>
       <c r="L61" t="n">
         <v>100</v>
@@ -3977,7 +3979,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -3989,7 +3991,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="L62" t="n">
         <v>100</v>
@@ -4036,11 +4038,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4048,7 +4050,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>19500</v>
+        <v>15600</v>
       </c>
       <c r="L63" t="n">
         <v>100</v>
@@ -4095,11 +4097,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4107,7 +4109,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>15600</v>
+        <v>32500</v>
       </c>
       <c r="L64" t="n">
         <v>100</v>
@@ -4154,7 +4156,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4213,7 +4215,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4239,7 +4241,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-03 12:54:44</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4247,17 +4249,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4267,31 +4269,31 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>32500</v>
+        <v>200000</v>
       </c>
       <c r="L67" t="n">
         <v>100</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
         </is>
       </c>
     </row>
@@ -4331,26 +4333,26 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="L68" t="n">
         <v>100</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4387,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4398,18 +4400,18 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="L69" t="n">
         <v>100</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
         </is>
       </c>
     </row>
@@ -4444,31 +4446,31 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>1600000</v>
+        <v>350000</v>
       </c>
       <c r="L70" t="n">
         <v>100</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
         </is>
       </c>
     </row>
@@ -4503,38 +4505,38 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>350000</v>
+        <v>3250000</v>
       </c>
       <c r="L71" t="n">
         <v>100</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:44</t>
+          <t>2026-10-03 13:04:08</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4542,12 +4544,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4562,12 +4564,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4575,18 +4577,18 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>3250000</v>
+        <v>1600000</v>
       </c>
       <c r="L72" t="n">
         <v>100</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
         </is>
       </c>
     </row>
@@ -4596,10 +4598,8 @@
           <t>2026-10-03 13:04:08</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B73" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4636,18 +4636,18 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="L73" t="n">
         <v>100</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
         </is>
       </c>
     </row>
@@ -4657,10 +4657,8 @@
           <t>2026-10-03 13:04:08</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B74" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4684,31 +4682,31 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="L74" t="n">
         <v>100</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet untuk Pop Joint</t>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
         </is>
       </c>
     </row>
@@ -4718,10 +4716,8 @@
           <t>2026-10-03 13:04:08</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B75" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4745,31 +4741,31 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>350000</v>
+        <v>200000</v>
       </c>
       <c r="L75" t="n">
         <v>100</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
         </is>
       </c>
     </row>
@@ -4779,10 +4775,8 @@
           <t>2026-10-03 13:04:08</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B76" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4806,92 +4800,1471 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>200000</v>
+        <v>3250000</v>
       </c>
       <c r="L76" t="n">
         <v>100</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-03 13:04:08</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Indocafe Coffemix Renteng</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>5</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L77" t="n">
+        <v>100</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>6</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>84500</v>
+      </c>
+      <c r="L78" t="n">
+        <v>100</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Nescafe Classic renteng</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L79" t="n">
+        <v>100</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>72</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L80" t="n">
+        <v>100</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>10</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L81" t="n">
+        <v>100</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>72</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L82" t="n">
+        <v>100</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>72</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L83" t="n">
+        <v>100</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>72</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L84" t="n">
+        <v>100</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>48</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L85" t="n">
+        <v>100</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>10</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L86" t="n">
+        <v>100</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>10</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L87" t="n">
+        <v>100</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:36</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>10</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L88" t="n">
+        <v>100</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>7201250141</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>04 Aug 2026</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>ESTIMATED SUM</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Trip</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="L77" t="n">
-        <v>100</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Indocafe Coffemix Renteng</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>5</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L89" t="n">
+        <v>100</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>6</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>84500</v>
+      </c>
+      <c r="L90" t="n">
+        <v>100</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Nescafe Classic renteng</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L91" t="n">
+        <v>100</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>72</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L92" t="n">
+        <v>100</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>10</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L93" t="n">
+        <v>100</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>72</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L94" t="n">
+        <v>100</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>72</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L95" t="n">
+        <v>100</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>72</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L96" t="n">
+        <v>100</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>48</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L97" t="n">
+        <v>100</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>10</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L98" t="n">
+        <v>100</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>10</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L99" t="n">
+        <v>100</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:36</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>10</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L100" t="n">
+        <v>100</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5542,10 +5542,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B89" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -5603,10 +5601,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B90" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -5664,10 +5660,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B91" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -5725,10 +5719,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B92" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -5786,10 +5778,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B93" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -5847,10 +5837,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B94" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -5908,10 +5896,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B95" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -5969,10 +5955,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B96" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -6030,10 +6014,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B97" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -6091,10 +6073,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B98" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -6152,10 +6132,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B99" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -6213,10 +6191,8 @@
           <t>2026-10-05 09:44:36</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B100" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -6265,6 +6241,1255 @@
       <c r="M100" t="inlineStr">
         <is>
           <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:50:37</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, main course</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>3195</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L101" t="n">
+        <v>100</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:50:37</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>1486.5</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L102" t="n">
+        <v>100</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:07:18</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>040/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>30</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L103" t="n">
+        <v>100</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:34:26</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>30</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L104" t="n">
+        <v>100</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:34:26</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>30</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L105" t="n">
+        <v>100</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:34:26</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>30</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L106" t="n">
+        <v>100</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:19:02</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>30</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L107" t="n">
+        <v>100</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:19:02</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>30</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L108" t="n">
+        <v>100</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:19:02</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>30</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>650000</v>
+      </c>
+      <c r="L109" t="n">
+        <v>100</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>RIgger Crane Shift Siang atas Nama Tison</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:19:02</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>30</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>650000</v>
+      </c>
+      <c r="L110" t="n">
+        <v>100</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:19:02</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>30</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>600000</v>
+      </c>
+      <c r="L111" t="n">
+        <v>100</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:19:02</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>30</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>600000</v>
+      </c>
+      <c r="L112" t="n">
+        <v>100</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:41:22</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>30</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L113" t="n">
+        <v>100</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:33:56</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>044/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>11 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>48</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L114" t="n">
+        <v>100</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:56:03</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>30</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="L115" t="n">
+        <v>100</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:56:03</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>30</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="L116" t="n">
+        <v>100</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:24:09</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>30</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L117" t="n">
+        <v>100</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:24:09</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>30</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L118" t="n">
+        <v>100</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:24:09</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>4</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L119" t="n">
+        <v>100</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:24:09</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>30</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L120" t="n">
+        <v>100</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:24:09</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>30</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L121" t="n">
+        <v>100</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7194,10 +7194,8 @@
           <t>2026-10-06 13:24:09</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B117" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -7255,10 +7253,8 @@
           <t>2026-10-06 13:24:09</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B118" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -7316,10 +7312,8 @@
           <t>2026-10-06 13:24:09</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B119" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -7377,10 +7371,8 @@
           <t>2026-10-06 13:24:09</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B120" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -7438,10 +7430,8 @@
           <t>2026-10-06 13:24:09</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B121" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -7490,6 +7480,244 @@
       <c r="M121" t="inlineStr">
         <is>
           <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:53:04</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>048/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>458.4</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L122" t="n">
+        <v>100</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:52:12</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>049/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Aqua 600 ml</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>2188</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>7500</v>
+      </c>
+      <c r="L123" t="n">
+        <v>100</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:52:12</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>049/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Aqua Galon Segel</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>15</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>53300</v>
+      </c>
+      <c r="L124" t="n">
+        <v>100</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:04:38</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>050/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L125" t="n">
+        <v>100</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7666,10 +7666,8 @@
           <t>2026-10-06 19:04:38</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B125" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -7718,6 +7716,372 @@
       <c r="M125" t="inlineStr">
         <is>
           <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:31</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="L126" t="n">
+        <v>100</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:31</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="L127" t="n">
+        <v>100</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:31</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L128" t="n">
+        <v>100</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:31</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L129" t="n">
+        <v>100</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:31</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="L130" t="n">
+        <v>100</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:31</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="L131" t="n">
+        <v>100</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7725,10 +7725,8 @@
           <t>2026-10-07 06:11:31</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B126" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -7786,10 +7784,8 @@
           <t>2026-10-07 06:11:31</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B127" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -7847,10 +7843,8 @@
           <t>2026-10-07 06:11:31</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B128" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -7908,10 +7902,8 @@
           <t>2026-10-07 06:11:31</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B129" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -7969,10 +7961,8 @@
           <t>2026-10-07 06:11:31</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B130" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -8030,10 +8020,8 @@
           <t>2026-10-07 06:11:31</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B131" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -8082,6 +8070,842 @@
       <c r="M131" t="inlineStr">
         <is>
           <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:42:21</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="L132" t="n">
+        <v>100</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:42:21</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="L133" t="n">
+        <v>100</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:00:43</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="L134" t="n">
+        <v>100</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:00:43</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="L135" t="n">
+        <v>100</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:32:35</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>29 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="L136" t="n">
+        <v>100</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:32:35</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>29 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="L137" t="n">
+        <v>100</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:32:35</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>29 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="L138" t="n">
+        <v>100</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:32:35</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>29 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="L139" t="n">
+        <v>100</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:32:35</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>29 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="L140" t="n">
+        <v>100</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:41:27</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="L141" t="n">
+        <v>100</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:41:27</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="L142" t="n">
+        <v>100</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:41:27</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="L143" t="n">
+        <v>100</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:41:27</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="L144" t="n">
+        <v>100</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:41:27</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="L145" t="n">
+        <v>100</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6247,7 +6247,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-06 09:50:37</t>
+          <t>2026-10-06 10:07:18</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6275,38 +6275,38 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>65000</v>
+        <v>750000</v>
       </c>
       <c r="L101" t="n">
         <v>100</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-06 09:50:37</t>
+          <t>2026-10-06 10:34:26</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6334,38 +6334,38 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1486.5</v>
+        <v>30</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>33000</v>
+        <v>500000</v>
       </c>
       <c r="L102" t="n">
         <v>100</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-06 10:07:18</t>
+          <t>2026-10-06 10:34:26</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -6410,14 +6410,14 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="L103" t="n">
         <v>100</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
         </is>
       </c>
     </row>
@@ -6476,14 +6476,14 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-10-06 10:34:26</t>
+          <t>2026-10-06 11:19:02</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -6528,21 +6528,21 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="L105" t="n">
         <v>100</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
+          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-10-06 10:34:26</t>
+          <t>2026-10-06 11:19:02</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -6587,14 +6587,14 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="L106" t="n">
         <v>100</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
+          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -6646,14 +6646,14 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="L107" t="n">
         <v>100</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
+          <t>RIgger Crane Shift Siang atas Nama Tison</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6705,14 +6705,14 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="L108" t="n">
         <v>100</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -6764,14 +6764,14 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="L109" t="n">
         <v>100</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>RIgger Crane Shift Siang atas Nama Tison</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6823,21 +6823,21 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="L110" t="n">
         <v>100</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:02</t>
+          <t>2026-10-06 11:41:22</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -6882,21 +6882,21 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="L111" t="n">
         <v>100</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:02</t>
+          <t>2026-10-06 12:33:56</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>11 Sep 2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6929,33 +6929,33 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>600000</v>
+        <v>250000</v>
       </c>
       <c r="L112" t="n">
         <v>100</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
+          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-06 11:41:22</t>
+          <t>2026-10-06 12:56:03</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -7000,21 +7000,21 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>500000</v>
+        <v>8500000</v>
       </c>
       <c r="L113" t="n">
         <v>100</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
+          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33:56</t>
+          <t>2026-10-06 12:56:03</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>11 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7042,38 +7042,38 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>250000</v>
+        <v>2750000</v>
       </c>
       <c r="L114" t="n">
         <v>100</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-06 12:56:03</t>
+          <t>2026-10-06 13:24:09</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -7118,21 +7118,21 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>8500000</v>
+        <v>1600000</v>
       </c>
       <c r="L115" t="n">
         <v>100</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-06 12:56:03</t>
+          <t>2026-10-06 13:24:09</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -7177,14 +7177,14 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>2750000</v>
+        <v>1600000</v>
       </c>
       <c r="L116" t="n">
         <v>100</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -7342,11 +7342,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -7361,14 +7361,14 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-06 13:24:09</t>
+          <t>2026-10-06 17:53:04</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7396,38 +7396,38 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>30</v>
+        <v>458.4</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="L120" t="n">
         <v>100</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-06 13:24:09</t>
+          <t>2026-10-06 18:52:12</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7455,38 +7455,38 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>30</v>
+        <v>2188</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="L121" t="n">
         <v>100</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-06 17:53:04</t>
+          <t>2026-10-06 18:52:12</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7514,38 +7514,38 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>458.4</v>
+        <v>15</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>25000</v>
+        <v>53300</v>
       </c>
       <c r="L122" t="n">
         <v>100</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-06 18:52:12</t>
+          <t>2026-10-06 19:04:38</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7573,38 +7573,38 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2188</v>
+        <v>1</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K123" t="n">
-        <v>7500</v>
+        <v>60000000</v>
       </c>
       <c r="L123" t="n">
         <v>100</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-06 18:52:12</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7632,38 +7632,38 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>53300</v>
+        <v>25000000</v>
       </c>
       <c r="L124" t="n">
         <v>100</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-06 19:04:38</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -7704,18 +7704,18 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>60000000</v>
+        <v>17500000</v>
       </c>
       <c r="L125" t="n">
         <v>100</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -7750,12 +7750,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -7767,14 +7767,14 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>25000000</v>
+        <v>60000000</v>
       </c>
       <c r="L126" t="n">
         <v>100</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -7826,14 +7826,14 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="L127" t="n">
         <v>100</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -7885,14 +7885,14 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="L128" t="n">
         <v>100</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -7944,7 +7944,7 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="L129" t="n">
         <v>100</v>
@@ -7958,7 +7958,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-07 08:42:21</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -7999,25 +7999,25 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>15000000</v>
+        <v>7500000</v>
       </c>
       <c r="L130" t="n">
         <v>100</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-07 08:42:21</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -8058,25 +8058,25 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>15000000</v>
+        <v>7500000</v>
       </c>
       <c r="L131" t="n">
         <v>100</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:21</t>
+          <t>2026-10-07 09:00:43</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -8121,21 +8121,21 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>7500000</v>
+        <v>7600000</v>
       </c>
       <c r="L132" t="n">
         <v>100</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:21</t>
+          <t>2026-10-07 09:00:43</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -8180,21 +8180,21 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>7500000</v>
+        <v>7600000</v>
       </c>
       <c r="L133" t="n">
         <v>100</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:43</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -8239,21 +8239,21 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>7600000</v>
+        <v>5290000</v>
       </c>
       <c r="L134" t="n">
         <v>100</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:43</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -8298,14 +8298,14 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>7600000</v>
+        <v>5290000</v>
       </c>
       <c r="L135" t="n">
         <v>100</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -8357,14 +8357,14 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="L136" t="n">
         <v>100</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -8416,14 +8416,14 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="L137" t="n">
         <v>100</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -8482,14 +8482,14 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -8534,21 +8534,21 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>6555000</v>
+        <v>5290000</v>
       </c>
       <c r="L139" t="n">
         <v>100</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -8589,18 +8589,18 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>6555000</v>
+        <v>5290000</v>
       </c>
       <c r="L140" t="n">
         <v>100</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
@@ -8610,10 +8610,8 @@
           <t>2026-10-07 10:41:27</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B141" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -8642,7 +8640,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -8654,14 +8652,14 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="L141" t="n">
         <v>100</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
     </row>
@@ -8671,10 +8669,8 @@
           <t>2026-10-07 10:41:27</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B142" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -8698,12 +8694,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -8715,14 +8711,14 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="L142" t="n">
         <v>100</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
@@ -8732,10 +8728,8 @@
           <t>2026-10-07 10:41:27</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B143" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -8759,12 +8753,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -8772,40 +8766,38 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="L143" t="n">
         <v>100</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-07 11:27:28</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8844,29 +8836,27 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
+          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-07 11:27:28</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8894,7 +8884,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -8905,7 +8895,188 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
+          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:27:28</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>29 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>5520000</v>
+      </c>
+      <c r="L146" t="n">
+        <v>100</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:57:48</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, main course</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>3195</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L147" t="n">
+        <v>100</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:57:48</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>1488</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L148" t="n">
+        <v>100</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -7073,7 +7073,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-06 13:24:09</t>
+          <t>2026-10-06 17:53:04</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7101,38 +7101,38 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>30</v>
+        <v>458.4</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K115" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="L115" t="n">
         <v>100</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-06 13:24:09</t>
+          <t>2026-10-06 18:52:12</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7160,38 +7160,38 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>30</v>
+        <v>2188</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="L116" t="n">
         <v>100</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-06 13:24:09</t>
+          <t>2026-10-06 18:52:12</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7219,38 +7219,38 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>1600000</v>
+        <v>53300</v>
       </c>
       <c r="L117" t="n">
         <v>100</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-06 13:24:09</t>
+          <t>2026-10-06 19:04:38</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7278,38 +7278,38 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>1600000</v>
+        <v>60000000</v>
       </c>
       <c r="L118" t="n">
         <v>100</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-06 13:24:09</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7337,38 +7337,38 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>1600000</v>
+        <v>25000000</v>
       </c>
       <c r="L119" t="n">
         <v>100</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-06 17:53:04</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7401,33 +7401,33 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>458.4</v>
+        <v>1</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>25000</v>
+        <v>17500000</v>
       </c>
       <c r="L120" t="n">
         <v>100</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-06 18:52:12</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7455,38 +7455,38 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2188</v>
+        <v>1</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>7500</v>
+        <v>60000000</v>
       </c>
       <c r="L121" t="n">
         <v>100</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-06 18:52:12</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7514,38 +7514,38 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>53300</v>
+        <v>60000000</v>
       </c>
       <c r="L122" t="n">
         <v>100</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-06 19:04:38</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -7586,18 +7586,18 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K123" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="L123" t="n">
         <v>100</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -7632,12 +7632,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -7649,21 +7649,21 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>25000000</v>
+        <v>15000000</v>
       </c>
       <c r="L124" t="n">
         <v>100</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-07 08:42:21</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -7704,25 +7704,25 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>17500000</v>
+        <v>7500000</v>
       </c>
       <c r="L125" t="n">
         <v>100</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-07 08:42:21</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -7763,25 +7763,25 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>60000000</v>
+        <v>7500000</v>
       </c>
       <c r="L126" t="n">
         <v>100</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-07 09:00:43</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -7789,17 +7789,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -7822,25 +7822,25 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>60000000</v>
+        <v>7600000</v>
       </c>
       <c r="L127" t="n">
         <v>100</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-07 09:00:43</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -7848,17 +7848,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K128" t="n">
-        <v>15000000</v>
+        <v>7600000</v>
       </c>
       <c r="L128" t="n">
         <v>100</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -7907,17 +7907,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7927,12 +7927,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -7940,25 +7940,25 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>15000000</v>
+        <v>5290000</v>
       </c>
       <c r="L129" t="n">
         <v>100</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:21</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -8003,21 +8003,21 @@
         </is>
       </c>
       <c r="K130" t="n">
-        <v>7500000</v>
+        <v>5290000</v>
       </c>
       <c r="L130" t="n">
         <v>100</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:21</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -8025,17 +8025,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -8062,21 +8062,21 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>7500000</v>
+        <v>6555000</v>
       </c>
       <c r="L131" t="n">
         <v>100</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:43</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -8121,21 +8121,21 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>7600000</v>
+        <v>6555000</v>
       </c>
       <c r="L132" t="n">
         <v>100</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:43</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -8176,25 +8176,25 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K133" t="n">
-        <v>7600000</v>
+        <v>6555000</v>
       </c>
       <c r="L133" t="n">
         <v>100</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -8246,14 +8246,14 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -8312,7 +8312,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -8364,14 +8364,14 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="L137" t="n">
         <v>100</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -8475,21 +8475,21 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="L138" t="n">
         <v>100</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
+          <t>2026-10-07 11:27:28</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -8534,21 +8534,21 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="L139" t="n">
         <v>100</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
+          <t>2026-10-07 11:27:28</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -8593,21 +8593,21 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="L140" t="n">
         <v>100</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
+          <t>2026-10-07 11:27:28</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -8652,21 +8652,21 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>6555000</v>
+        <v>5520000</v>
       </c>
       <c r="L141" t="n">
         <v>100</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
+          <t>2026-10-07 11:57:48</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -8674,17 +8674,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -8699,33 +8699,33 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>3195</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>7600000</v>
+        <v>65000</v>
       </c>
       <c r="L142" t="n">
         <v>100</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
+          <t>2026-10-07 11:57:48</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8758,11 +8758,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>1488</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -8770,39 +8770,41 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>7600000</v>
+        <v>33000</v>
       </c>
       <c r="L143" t="n">
         <v>100</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:28</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:57:22</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8812,56 +8814,58 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>7600000</v>
+        <v>1600000</v>
       </c>
       <c r="L144" t="n">
         <v>100</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:28</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:57:22</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8871,56 +8875,58 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>7600000</v>
+        <v>1600000</v>
       </c>
       <c r="L145" t="n">
         <v>100</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:28</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:57:22</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8930,38 +8936,38 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K146" t="n">
-        <v>5520000</v>
+        <v>1600000</v>
       </c>
       <c r="L146" t="n">
         <v>100</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-07 11:57:48</t>
+          <t>2026-10-10 08:57:22</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8971,7 +8977,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8991,38 +8997,38 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K147" t="n">
-        <v>65000</v>
+        <v>1600000</v>
       </c>
       <c r="L147" t="n">
         <v>100</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-07 11:57:48</t>
+          <t>2026-10-10 08:57:22</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9032,7 +9038,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9052,31 +9058,31 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1488</v>
+        <v>30</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K148" t="n">
-        <v>33000</v>
+        <v>1600000</v>
       </c>
       <c r="L148" t="n">
         <v>100</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8787,10 +8787,8 @@
           <t>2026-10-10 08:57:22</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B144" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -8848,10 +8846,8 @@
           <t>2026-10-10 08:57:22</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B145" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -8909,10 +8905,8 @@
           <t>2026-10-10 08:57:22</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B146" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -8970,10 +8964,8 @@
           <t>2026-10-10 08:57:22</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B147" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -9031,10 +9023,8 @@
           <t>2026-10-10 08:57:22</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B148" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -9083,6 +9073,126 @@
       <c r="M148" t="inlineStr">
         <is>
           <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:27:09</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="L149" t="n">
+        <v>100</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:35:46</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>052/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="L150" t="n">
+        <v>100</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9141,10 +9141,8 @@
           <t>2026-10-13 10:35:46</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B150" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -9193,6 +9191,246 @@
       <c r="M150" t="inlineStr">
         <is>
           <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:24:10</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>30 Jan 2026</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>4500011794</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>50</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L151" t="n">
+        <v>100</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:24:10</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>30 Jan 2026</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>4500011794</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>50</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L152" t="n">
+        <v>100</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:53:53</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>4500011795</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>2</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>175000</v>
+      </c>
+      <c r="L153" t="n">
+        <v>100</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:53:53</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>4500011795</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L154" t="n">
+        <v>100</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8666,7 +8666,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-07 11:57:48</t>
+          <t>2026-10-10 08:57:22</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8694,38 +8694,38 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>65000</v>
+        <v>1600000</v>
       </c>
       <c r="L142" t="n">
         <v>100</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-07 11:57:48</t>
+          <t>2026-10-10 08:57:22</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8753,31 +8753,31 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1488</v>
+        <v>30</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>33000</v>
+        <v>1600000</v>
       </c>
       <c r="L143" t="n">
         <v>100</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
@@ -8935,11 +8935,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:22</t>
+          <t>2026-10-13 10:27:09</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -8969,17 +8969,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>14 Aug 2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8989,38 +8989,38 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K147" t="n">
-        <v>1600000</v>
+        <v>1500000</v>
       </c>
       <c r="L147" t="n">
         <v>100</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:22</t>
+          <t>2026-10-13 10:35:46</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -9028,17 +9028,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>15 Sep 2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9048,38 +9048,38 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K148" t="n">
-        <v>1600000</v>
+        <v>7500000</v>
       </c>
       <c r="L148" t="n">
         <v>100</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-10-13 10:27:09</t>
+          <t>2026-10-14 13:24:10</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -9087,17 +9087,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9116,29 +9116,29 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>1500000</v>
+        <v>10000</v>
       </c>
       <c r="L149" t="n">
         <v>100</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-10-13 10:35:46</t>
+          <t>2026-10-14 13:24:10</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -9146,17 +9146,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>15 Sep 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9175,29 +9175,29 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K150" t="n">
-        <v>7500000</v>
+        <v>15000</v>
       </c>
       <c r="L150" t="n">
         <v>100</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-10-14 13:24:10</t>
+          <t>2026-10-14 13:53:53</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -9205,17 +9205,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9234,29 +9234,29 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K151" t="n">
-        <v>10000</v>
+        <v>175000</v>
       </c>
       <c r="L151" t="n">
         <v>100</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-10-14 13:24:10</t>
+          <t>2026-10-14 13:53:53</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -9264,17 +9264,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9293,49 +9293,47 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K152" t="n">
-        <v>15000</v>
+        <v>100000</v>
       </c>
       <c r="L152" t="n">
         <v>100</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-10-14 13:53:53</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-15 17:38:23</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9345,92 +9343,212 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>2578</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K153" t="n">
-        <v>175000</v>
+        <v>65000</v>
       </c>
       <c r="L153" t="n">
         <v>100</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-10-14 13:53:53</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
+          <t>2026-10-15 17:38:23</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Operational side consumption</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1157</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L154" t="n">
+        <v>100</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:44:54</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
         <is>
           <t>7201250141</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>04 Sep 2026</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>4500011795</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>PROVISIONAL SUM</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>At Cost + Fee 15%</t>
-        </is>
-      </c>
-      <c r="I154" t="n">
-        <v>1</v>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Ea</t>
-        </is>
-      </c>
-      <c r="K154" t="n">
-        <v>100000</v>
-      </c>
-      <c r="L154" t="n">
-        <v>100</v>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>operational consumption</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>3195</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L155" t="n">
+        <v>100</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:44:54</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Operational side consumption</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>1488</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L156" t="n">
+        <v>100</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2825,7 +2825,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 12:54:44</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2853,38 +2853,38 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>32500</v>
+        <v>200000</v>
       </c>
       <c r="L43" t="n">
         <v>100</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 12:54:44</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2892,17 +2892,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2912,38 +2912,38 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>84500</v>
+        <v>250000</v>
       </c>
       <c r="L44" t="n">
         <v>100</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 12:54:44</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2971,38 +2971,38 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>26000</v>
+        <v>1600000</v>
       </c>
       <c r="L45" t="n">
         <v>100</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 12:54:44</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -3010,17 +3010,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3030,38 +3030,38 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9750</v>
+        <v>350000</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 12:54:44</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3094,33 +3094,33 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>19500</v>
+        <v>3250000</v>
       </c>
       <c r="L47" t="n">
         <v>100</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 13:04:08</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3128,17 +3128,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3148,38 +3148,38 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>13000</v>
+        <v>1600000</v>
       </c>
       <c r="L48" t="n">
         <v>100</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 13:04:08</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3207,38 +3207,38 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>9750</v>
+        <v>250000</v>
       </c>
       <c r="L49" t="n">
         <v>100</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 13:04:08</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3246,17 +3246,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3266,38 +3266,38 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>19500</v>
+        <v>350000</v>
       </c>
       <c r="L50" t="n">
         <v>100</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 13:04:08</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3325,38 +3325,38 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>32500</v>
+        <v>200000</v>
       </c>
       <c r="L51" t="n">
         <v>100</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-03 13:04:08</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3364,17 +3364,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3389,33 +3389,33 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>32500</v>
+        <v>3250000</v>
       </c>
       <c r="L52" t="n">
         <v>100</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-06 10:07:18</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3423,17 +3423,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3443,38 +3443,38 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>32500</v>
+        <v>750000</v>
       </c>
       <c r="L53" t="n">
         <v>100</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-03 06:53:35</t>
+          <t>2026-10-06 10:34:26</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3482,17 +3482,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3502,38 +3502,38 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>15600</v>
+        <v>500000</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 10:34:26</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3561,38 +3561,38 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>32500</v>
+        <v>500000</v>
       </c>
       <c r="L55" t="n">
         <v>100</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 10:34:26</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3600,17 +3600,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3620,38 +3620,38 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>84500</v>
+        <v>500000</v>
       </c>
       <c r="L56" t="n">
         <v>100</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 11:19:02</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3679,38 +3679,38 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>26000</v>
+        <v>750000</v>
       </c>
       <c r="L57" t="n">
         <v>100</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 11:19:02</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3718,17 +3718,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3738,38 +3738,38 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>9750</v>
+        <v>750000</v>
       </c>
       <c r="L58" t="n">
         <v>100</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 11:19:02</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3777,17 +3777,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3797,38 +3797,38 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>19500</v>
+        <v>650000</v>
       </c>
       <c r="L59" t="n">
         <v>100</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>RIgger Crane Shift Siang atas Nama Tison</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 11:19:02</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3856,38 +3856,38 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>13000</v>
+        <v>650000</v>
       </c>
       <c r="L60" t="n">
         <v>100</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 11:19:02</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3915,38 +3915,38 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>9750</v>
+        <v>600000</v>
       </c>
       <c r="L61" t="n">
         <v>100</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 11:19:02</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3954,17 +3954,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3974,38 +3974,38 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>19500</v>
+        <v>600000</v>
       </c>
       <c r="L62" t="n">
         <v>100</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 11:41:22</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4033,38 +4033,38 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>15600</v>
+        <v>500000</v>
       </c>
       <c r="L63" t="n">
         <v>100</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 12:33:56</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>11 Sep 2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4092,38 +4092,38 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>32500</v>
+        <v>250000</v>
       </c>
       <c r="L64" t="n">
         <v>100</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 12:56:03</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4151,38 +4151,38 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>32500</v>
+        <v>8500000</v>
       </c>
       <c r="L65" t="n">
         <v>100</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:10</t>
+          <t>2026-10-06 12:56:03</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -4190,17 +4190,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4210,38 +4210,38 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>32500</v>
+        <v>2750000</v>
       </c>
       <c r="L66" t="n">
         <v>100</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:44</t>
+          <t>2026-10-06 17:53:04</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4249,17 +4249,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4269,16 +4269,16 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>458.4</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>200000</v>
+        <v>25000</v>
       </c>
       <c r="L67" t="n">
         <v>100</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:44</t>
+          <t>2026-10-06 18:52:12</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4328,38 +4328,38 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2188</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>250000</v>
+        <v>7500</v>
       </c>
       <c r="L68" t="n">
         <v>100</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:44</t>
+          <t>2026-10-06 18:52:12</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4387,38 +4387,38 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>1600000</v>
+        <v>53300</v>
       </c>
       <c r="L69" t="n">
         <v>100</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:44</t>
+          <t>2026-10-06 19:04:38</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4446,38 +4446,38 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>350000</v>
+        <v>60000000</v>
       </c>
       <c r="L70" t="n">
         <v>100</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:44</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4485,17 +4485,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4518,25 +4518,25 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>3250000</v>
+        <v>25000000</v>
       </c>
       <c r="L71" t="n">
         <v>100</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-03 13:04:08</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4544,17 +4544,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4577,25 +4577,25 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>1600000</v>
+        <v>17500000</v>
       </c>
       <c r="L72" t="n">
         <v>100</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-03 13:04:08</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -4603,17 +4603,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4636,25 +4636,25 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>250000</v>
+        <v>60000000</v>
       </c>
       <c r="L73" t="n">
         <v>100</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet untuk Pop Joint</t>
+          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-03 13:04:08</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -4662,17 +4662,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4682,38 +4682,38 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>350000</v>
+        <v>60000000</v>
       </c>
       <c r="L74" t="n">
         <v>100</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-03 13:04:08</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4741,38 +4741,38 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>200000</v>
+        <v>15000000</v>
       </c>
       <c r="L75" t="n">
         <v>100</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-03 13:04:08</t>
+          <t>2026-10-07 06:11:31</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4780,17 +4780,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4813,25 +4813,25 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>3250000</v>
+        <v>15000000</v>
       </c>
       <c r="L76" t="n">
         <v>100</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 09:00:43</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4839,17 +4839,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4859,38 +4859,38 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>32500</v>
+        <v>7600000</v>
       </c>
       <c r="L77" t="n">
         <v>100</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 09:00:43</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -4898,17 +4898,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4918,38 +4918,38 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>84500</v>
+        <v>7600000</v>
       </c>
       <c r="L78" t="n">
         <v>100</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4957,17 +4957,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4977,38 +4977,38 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>26000</v>
+        <v>5290000</v>
       </c>
       <c r="L79" t="n">
         <v>100</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5036,38 +5036,38 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>9750</v>
+        <v>5290000</v>
       </c>
       <c r="L80" t="n">
         <v>100</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -5075,17 +5075,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5095,38 +5095,38 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>19500</v>
+        <v>6555000</v>
       </c>
       <c r="L81" t="n">
         <v>100</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -5134,17 +5134,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5154,38 +5154,38 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>13000</v>
+        <v>6555000</v>
       </c>
       <c r="L82" t="n">
         <v>100</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 09:32:35</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -5193,17 +5193,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5213,38 +5213,38 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>9750</v>
+        <v>6555000</v>
       </c>
       <c r="L83" t="n">
         <v>100</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -5252,17 +5252,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5272,38 +5272,38 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>19500</v>
+        <v>5290000</v>
       </c>
       <c r="L84" t="n">
         <v>100</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -5311,17 +5311,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5331,38 +5331,38 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>15600</v>
+        <v>5290000</v>
       </c>
       <c r="L85" t="n">
         <v>100</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5390,38 +5390,38 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>32500</v>
+        <v>6555000</v>
       </c>
       <c r="L86" t="n">
         <v>100</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -5429,17 +5429,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5449,38 +5449,38 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>32500</v>
+        <v>7600000</v>
       </c>
       <c r="L87" t="n">
         <v>100</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:36</t>
+          <t>2026-10-07 10:41:27</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -5488,17 +5488,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5508,38 +5508,38 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>32500</v>
+        <v>7600000</v>
       </c>
       <c r="L88" t="n">
         <v>100</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-07 11:27:28</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -5547,17 +5547,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5567,38 +5567,38 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>32500</v>
+        <v>7600000</v>
       </c>
       <c r="L89" t="n">
         <v>100</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-07 11:27:28</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -5606,17 +5606,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5626,38 +5626,38 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>84500</v>
+        <v>7600000</v>
       </c>
       <c r="L90" t="n">
         <v>100</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-07 11:27:28</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -5665,17 +5665,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>29 Aug 2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5685,38 +5685,38 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>26000</v>
+        <v>5520000</v>
       </c>
       <c r="L91" t="n">
         <v>100</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-10 08:57:22</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -5724,17 +5724,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5744,38 +5744,38 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>9750</v>
+        <v>1600000</v>
       </c>
       <c r="L92" t="n">
         <v>100</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-10 08:57:22</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -5783,17 +5783,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5803,38 +5803,38 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>19500</v>
+        <v>1600000</v>
       </c>
       <c r="L93" t="n">
         <v>100</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-10 08:57:22</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -5842,17 +5842,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5862,38 +5862,38 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>13000</v>
+        <v>1600000</v>
       </c>
       <c r="L94" t="n">
         <v>100</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-10 08:57:22</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -5901,17 +5901,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5921,38 +5921,38 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>9750</v>
+        <v>1600000</v>
       </c>
       <c r="L95" t="n">
         <v>100</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-10 08:57:22</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -5960,17 +5960,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5980,38 +5980,38 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>19500</v>
+        <v>1600000</v>
       </c>
       <c r="L96" t="n">
         <v>100</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-13 10:27:09</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -6019,17 +6019,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>14 Aug 2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6039,38 +6039,38 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>15600</v>
+        <v>1500000</v>
       </c>
       <c r="L97" t="n">
         <v>100</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-13 10:35:46</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -6078,17 +6078,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>15 Sep 2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6098,38 +6098,38 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>32500</v>
+        <v>7500000</v>
       </c>
       <c r="L98" t="n">
         <v>100</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-14 13:24:10</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -6137,17 +6137,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6157,38 +6157,38 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>32500</v>
+        <v>10000</v>
       </c>
       <c r="L99" t="n">
         <v>100</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:36</t>
+          <t>2026-10-14 13:24:10</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -6196,17 +6196,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6216,38 +6216,38 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>32500</v>
+        <v>15000</v>
       </c>
       <c r="L100" t="n">
         <v>100</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-06 10:07:18</t>
+          <t>2026-10-14 13:53:53</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -6255,17 +6255,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6275,38 +6275,38 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>750000</v>
+        <v>175000</v>
       </c>
       <c r="L101" t="n">
         <v>100</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-06 10:34:26</t>
+          <t>2026-10-14 13:53:53</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -6314,17 +6314,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6334,38 +6334,38 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="L102" t="n">
         <v>100</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-06 10:34:26</t>
+          <t>2026-10-15 17:38:23</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6393,38 +6393,38 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>30</v>
+        <v>2578</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>500000</v>
+        <v>65000</v>
       </c>
       <c r="L103" t="n">
         <v>100</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-10-06 10:34:26</t>
+          <t>2026-10-15 17:38:23</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -6432,12 +6432,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6452,38 +6452,38 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operational side consumption</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>30</v>
+        <v>1157</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>500000</v>
+        <v>33000</v>
       </c>
       <c r="L104" t="n">
         <v>100</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:02</t>
+          <t>2026-10-15 17:44:54</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6511,38 +6511,38 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>30</v>
+        <v>3195</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>750000</v>
+        <v>65000</v>
       </c>
       <c r="L105" t="n">
         <v>100</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:02</t>
+          <t>2026-10-15 17:44:54</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6570,38 +6570,38 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Operational side consumption</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>30</v>
+        <v>1488</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>750000</v>
+        <v>33000</v>
       </c>
       <c r="L106" t="n">
         <v>100</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:02</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -6609,17 +6609,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6629,38 +6629,38 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>650000</v>
+        <v>32500</v>
       </c>
       <c r="L107" t="n">
         <v>100</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>RIgger Crane Shift Siang atas Nama Tison</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:02</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -6668,17 +6668,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6688,38 +6688,38 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>650000</v>
+        <v>84500</v>
       </c>
       <c r="L108" t="n">
         <v>100</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:02</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -6727,17 +6727,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6747,38 +6747,38 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>600000</v>
+        <v>26000</v>
       </c>
       <c r="L109" t="n">
         <v>100</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:02</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -6786,17 +6786,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6806,38 +6806,38 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K110" t="n">
-        <v>600000</v>
+        <v>9750</v>
       </c>
       <c r="L110" t="n">
         <v>100</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-10-06 11:41:22</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6865,38 +6865,38 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K111" t="n">
-        <v>500000</v>
+        <v>19500</v>
       </c>
       <c r="L111" t="n">
         <v>100</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33:56</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -6904,17 +6904,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>11 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6924,38 +6924,38 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>250000</v>
+        <v>13000</v>
       </c>
       <c r="L112" t="n">
         <v>100</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-06 12:56:03</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -6963,17 +6963,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6983,38 +6983,38 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K113" t="n">
-        <v>8500000</v>
+        <v>9750</v>
       </c>
       <c r="L113" t="n">
         <v>100</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10-06 12:56:03</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7042,38 +7042,38 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>2750000</v>
+        <v>19500</v>
       </c>
       <c r="L114" t="n">
         <v>100</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-06 17:53:04</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -7081,17 +7081,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7101,38 +7101,38 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>458.4</v>
+        <v>36</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K115" t="n">
-        <v>25000</v>
+        <v>32500</v>
       </c>
       <c r="L115" t="n">
         <v>100</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-06 18:52:12</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -7140,17 +7140,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7165,33 +7165,33 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2188</v>
+        <v>36</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>7500</v>
+        <v>32500</v>
       </c>
       <c r="L116" t="n">
         <v>100</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-06 18:52:12</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -7199,17 +7199,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7224,33 +7224,33 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>53300</v>
+        <v>32500</v>
       </c>
       <c r="L117" t="n">
         <v>100</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-06 19:04:38</t>
+          <t>2026-10-16 10:49:09</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -7258,17 +7258,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7278,16 +7278,16 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -7295,21 +7295,21 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>60000000</v>
+        <v>15600</v>
       </c>
       <c r="L118" t="n">
         <v>100</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -7317,17 +7317,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7337,38 +7337,38 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>25000000</v>
+        <v>32500</v>
       </c>
       <c r="L119" t="n">
         <v>100</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -7376,17 +7376,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7396,38 +7396,38 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>17500000</v>
+        <v>84500</v>
       </c>
       <c r="L120" t="n">
         <v>100</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -7435,17 +7435,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7455,38 +7455,38 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>60000000</v>
+        <v>26000</v>
       </c>
       <c r="L121" t="n">
         <v>100</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -7494,17 +7494,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7514,38 +7514,38 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>60000000</v>
+        <v>9750</v>
       </c>
       <c r="L122" t="n">
         <v>100</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -7553,17 +7553,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7573,38 +7573,38 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K123" t="n">
-        <v>15000000</v>
+        <v>19500</v>
       </c>
       <c r="L123" t="n">
         <v>100</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:31</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -7612,17 +7612,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7632,38 +7632,38 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>15000000</v>
+        <v>13000</v>
       </c>
       <c r="L124" t="n">
         <v>100</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:21</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -7671,17 +7671,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7691,38 +7691,38 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>7500000</v>
+        <v>9750</v>
       </c>
       <c r="L125" t="n">
         <v>100</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-07 08:42:21</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -7730,17 +7730,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7750,38 +7750,38 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>7500000</v>
+        <v>19500</v>
       </c>
       <c r="L126" t="n">
         <v>100</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:43</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -7789,17 +7789,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7809,38 +7809,38 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>7600000</v>
+        <v>15600</v>
       </c>
       <c r="L127" t="n">
         <v>100</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:43</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -7848,17 +7848,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7868,38 +7868,38 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K128" t="n">
-        <v>7600000</v>
+        <v>32500</v>
       </c>
       <c r="L128" t="n">
         <v>100</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -7907,17 +7907,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7927,38 +7927,38 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>5290000</v>
+        <v>32500</v>
       </c>
       <c r="L129" t="n">
         <v>100</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-16 10:58:27</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7986,38 +7986,38 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>5290000</v>
+        <v>32500</v>
       </c>
       <c r="L130" t="n">
         <v>100</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -8025,17 +8025,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8045,38 +8045,38 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>6555000</v>
+        <v>32500</v>
       </c>
       <c r="L131" t="n">
         <v>100</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -8084,17 +8084,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8104,38 +8104,38 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K132" t="n">
-        <v>6555000</v>
+        <v>84500</v>
       </c>
       <c r="L132" t="n">
         <v>100</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:35</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -8143,17 +8143,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8163,38 +8163,38 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K133" t="n">
-        <v>6555000</v>
+        <v>26000</v>
       </c>
       <c r="L133" t="n">
         <v>100</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8222,38 +8222,38 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K134" t="n">
-        <v>5290000</v>
+        <v>9750</v>
       </c>
       <c r="L134" t="n">
         <v>100</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -8261,17 +8261,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8281,38 +8281,38 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K135" t="n">
-        <v>5290000</v>
+        <v>19500</v>
       </c>
       <c r="L135" t="n">
         <v>100</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8340,38 +8340,38 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K136" t="n">
-        <v>6555000</v>
+        <v>13000</v>
       </c>
       <c r="L136" t="n">
         <v>100</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -8379,17 +8379,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8399,38 +8399,38 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K137" t="n">
-        <v>7600000</v>
+        <v>9750</v>
       </c>
       <c r="L137" t="n">
         <v>100</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:27</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -8438,17 +8438,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8458,38 +8458,38 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K138" t="n">
-        <v>7600000</v>
+        <v>19500</v>
       </c>
       <c r="L138" t="n">
         <v>100</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:28</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -8497,17 +8497,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8517,38 +8517,38 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K139" t="n">
-        <v>7600000</v>
+        <v>15600</v>
       </c>
       <c r="L139" t="n">
         <v>100</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:28</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -8556,17 +8556,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8576,38 +8576,38 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>7600000</v>
+        <v>32500</v>
       </c>
       <c r="L140" t="n">
         <v>100</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:28</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -8615,17 +8615,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>29 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8635,38 +8635,38 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>5520000</v>
+        <v>32500</v>
       </c>
       <c r="L141" t="n">
         <v>100</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:22</t>
+          <t>2026-10-16 11:08:16</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -8674,17 +8674,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -8694,38 +8694,38 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>1600000</v>
+        <v>32500</v>
       </c>
       <c r="L142" t="n">
         <v>100</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:22</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8753,38 +8753,38 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>1600000</v>
+        <v>32500</v>
       </c>
       <c r="L143" t="n">
         <v>100</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:22</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8812,38 +8812,38 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>1600000</v>
+        <v>84500</v>
       </c>
       <c r="L144" t="n">
         <v>100</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:22</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -8851,17 +8851,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8871,38 +8871,38 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>1600000</v>
+        <v>26000</v>
       </c>
       <c r="L145" t="n">
         <v>100</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:22</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -8910,17 +8910,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8930,38 +8930,38 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K146" t="n">
-        <v>1600000</v>
+        <v>9750</v>
       </c>
       <c r="L146" t="n">
         <v>100</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-13 10:27:09</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -8969,17 +8969,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8989,38 +8989,38 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K147" t="n">
-        <v>1500000</v>
+        <v>19500</v>
       </c>
       <c r="L147" t="n">
         <v>100</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-13 10:35:46</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -9028,17 +9028,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>15 Sep 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9048,38 +9048,38 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K148" t="n">
-        <v>7500000</v>
+        <v>13000</v>
       </c>
       <c r="L148" t="n">
         <v>100</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-10-14 13:24:10</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -9087,17 +9087,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9107,38 +9107,38 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>10000</v>
+        <v>9750</v>
       </c>
       <c r="L149" t="n">
         <v>100</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-10-14 13:24:10</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -9146,17 +9146,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9166,38 +9166,38 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K150" t="n">
-        <v>15000</v>
+        <v>19500</v>
       </c>
       <c r="L150" t="n">
         <v>100</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-10-14 13:53:53</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -9205,17 +9205,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9225,16 +9225,16 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -9242,21 +9242,21 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>175000</v>
+        <v>15600</v>
       </c>
       <c r="L151" t="n">
         <v>100</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-10-14 13:53:53</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -9264,17 +9264,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9284,16 +9284,16 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -9301,21 +9301,21 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>100000</v>
+        <v>32500</v>
       </c>
       <c r="L152" t="n">
         <v>100</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-10-15 17:38:23</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -9323,17 +9323,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9343,38 +9343,38 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>operational consumption</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2578</v>
+        <v>10</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K153" t="n">
-        <v>65000</v>
+        <v>32500</v>
       </c>
       <c r="L153" t="n">
         <v>100</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-10-15 17:38:23</t>
+          <t>2026-10-16 11:30:21</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9402,38 +9402,38 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Operational side consumption</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1157</v>
+        <v>10</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K154" t="n">
-        <v>33000</v>
+        <v>32500</v>
       </c>
       <c r="L154" t="n">
         <v>100</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-10-15 17:44:54</t>
+          <t>2026-10-16 11:49:49</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>30 Sep 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9463,16 +9463,16 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>operational consumption</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3195</v>
+        <v>4</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -9480,75 +9480,14 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>65000</v>
+        <v>7500000</v>
       </c>
       <c r="L155" t="n">
         <v>100</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-10-15 17:44:54</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>30 Sep 2026</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Operational side consumption</t>
-        </is>
-      </c>
-      <c r="I156" t="n">
-        <v>1488</v>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="K156" t="n">
-        <v>33000</v>
-      </c>
-      <c r="L156" t="n">
-        <v>100</v>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Mobilisasi 2 Unit Lighting Tower dan 2 Unit Mesin Genset 80 KVA dari Luwuk ke Senoro Cluster B</t>
         </is>
       </c>
     </row>
